--- a/src/test/java/resources/data.xlsx
+++ b/src/test/java/resources/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2497745_cognizant_com/Documents/Documents/HackathonProject/InsuranceAutomationHackathon/src/test/java/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDAF7DAF-EEF6-47C4-B7E6-721815F94A53}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B49B29E8-65F6-4B21-AE32-547C8C6831EA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Car" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,189 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+  <si>
+    <t>CityOfRegistration</t>
+  </si>
+  <si>
+    <t>CarMake</t>
+  </si>
+  <si>
+    <t>CarModel</t>
+  </si>
+  <si>
+    <t>MobileNumber</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>TAMILNADU-TIRUNELVELI</t>
+  </si>
+  <si>
+    <t>HYUNDAI</t>
+  </si>
+  <si>
+    <t>HYUNDAI - SANTRO ZIP PLUS LP (1086CC)</t>
+  </si>
+  <si>
+    <t>hyundai01@gmail.com</t>
+  </si>
+  <si>
+    <t>MAHARASHTRA-PUNE</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>MARUTI - WAGON R LXI-996CC (996CC)</t>
+  </si>
+  <si>
+    <t>maruti01@gmail.com</t>
+  </si>
+  <si>
+    <t>KARNATAKA-BENGALURU</t>
+  </si>
+  <si>
+    <t>TATA</t>
+  </si>
+  <si>
+    <t>TATA MOTORS - INDICA XETA GLS V2 BSIII (1396CC)</t>
+  </si>
+  <si>
+    <t>tata01@gmail.com</t>
+  </si>
+  <si>
+    <t>DELHI-NEW DELHI</t>
+  </si>
+  <si>
+    <t>MAHINDRA</t>
+  </si>
+  <si>
+    <t>MAHINDRA RENAULT PVT LTD. - LOGAN PETROL K7M PS E2 5 XF AIR BAG (1598CC)</t>
+  </si>
+  <si>
+    <t>mahindra01@gmail.com</t>
+  </si>
+  <si>
+    <t>GUJARAT-AHMEDABAD</t>
+  </si>
+  <si>
+    <t>HYUNDAI - GETZ PRIME GVS (1086CC)</t>
+  </si>
+  <si>
+    <t>hyundai02@gmail.com</t>
+  </si>
+  <si>
+    <t>KERALA-KOCHI</t>
+  </si>
+  <si>
+    <t>TATA MOTORS - TATA ESTATE (1948CC)</t>
+  </si>
+  <si>
+    <t>tata02@gmail.com</t>
+  </si>
+  <si>
+    <t>RAJASTHAN-JAIPUR</t>
+  </si>
+  <si>
+    <t>MARUTI - SX4 1.6 VXI (1586CC)</t>
+  </si>
+  <si>
+    <t>maruti02@gmail.com</t>
+  </si>
+  <si>
+    <t>TELANGANA-HYDERABAD</t>
+  </si>
+  <si>
+    <t>MAHINDRA RENAULT PVT LTD. - LOGAN DIESEL K9K PS E2 5 RT AIR BAG (1461CC)</t>
+  </si>
+  <si>
+    <t>mahindra02@gmail.com</t>
+  </si>
+  <si>
+    <t>WEST BENGAL-KOLKATA</t>
+  </si>
+  <si>
+    <t>HYUNDAI - SONATA EMBERA CRDI (1991CC)</t>
+  </si>
+  <si>
+    <t>hyundai03@gmail.com</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH-INDORE</t>
+  </si>
+  <si>
+    <t>TATA MOTORS - INDIGO MARINA GLE (1405CC)</t>
+  </si>
+  <si>
+    <t>tata03@gmail.com</t>
+  </si>
+  <si>
+    <t>UTTAR PRADESH-LUCKNOW</t>
+  </si>
+  <si>
+    <t>MARUTI - SX4 1.6 ZXI (1586CC)</t>
+  </si>
+  <si>
+    <t>maruti03@gmail.com</t>
+  </si>
+  <si>
+    <t>PUNJAB-CHANDIGARH</t>
+  </si>
+  <si>
+    <t>TATA MOTORS - INDIGO MARINA DICOR LX (1405CC)</t>
+  </si>
+  <si>
+    <t>tata04@gmail.com</t>
+  </si>
+  <si>
+    <t>ODISHA-BHUBANESWAR</t>
+  </si>
+  <si>
+    <t>HYUNDAI - GETZ PRIME GLE (1086CC)</t>
+  </si>
+  <si>
+    <t>hyundai04@gmail.com</t>
+  </si>
+  <si>
+    <t>BIHAR-PATNA</t>
+  </si>
+  <si>
+    <t>MAHINDRA RENAULT PVT LTD. - LOGAN PETROL K7M PS E2 5 JS AIR BAG (1598CC)</t>
+  </si>
+  <si>
+    <t>mahindra03@gmail.com</t>
+  </si>
+  <si>
+    <t>ASSAM-GUWAHATI</t>
+  </si>
+  <si>
+    <t>tata05@gmail.com</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -45,7 +222,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,12 +230,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -343,9 +539,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="34.54296875" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="3" max="3" width="81.1796875" customWidth="1"/>
+    <col min="4" max="4" width="39.453125" customWidth="1"/>
+    <col min="5" max="5" width="44.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2">
+        <v>9876543211</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>9876543212</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2">
+        <v>9876543213</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9876543214</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>9876543215</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2">
+        <v>9876543216</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2">
+        <v>9876543217</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9876543218</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2">
+        <v>9876543219</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9876543220</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2">
+        <v>9876543221</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2">
+        <v>9876543222</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2">
+        <v>9876543223</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2">
+        <v>9876543224</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/java/resources/data.xlsx
+++ b/src/test/java/resources/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2497745_cognizant_com/Documents/Documents/HackathonProject/InsuranceAutomationHackathon/src/test/java/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2497728_cognizant_com/Documents/Documents/AutomationProject/PolicyBazzarAutomationHackathon/src/test/java/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B49B29E8-65F6-4B21-AE32-547C8C6831EA}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3518FAB1-7ACA-4389-A734-02A703757C13}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Car" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>CityOfRegistration</t>
   </si>
@@ -186,13 +186,160 @@
   </si>
   <si>
     <t>tata05@gmail.com</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>StartDate</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>5, Sept 2026</t>
+  </si>
+  <si>
+    <t>30, Nov 2026</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>12, Oct 2026</t>
+  </si>
+  <si>
+    <t>25, Oct 2026</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>1, Jan 2027</t>
+  </si>
+  <si>
+    <t>15, Jan 2027</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>18, Feb 2027</t>
+  </si>
+  <si>
+    <t>28, Feb 2027</t>
+  </si>
+  <si>
+    <t>7, March 2027</t>
+  </si>
+  <si>
+    <t>22, March 2027</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>10, April 2027</t>
+  </si>
+  <si>
+    <t>20, April 2027</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>5, May 2027</t>
+  </si>
+  <si>
+    <t>18, May 2027</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>14, June 2027</t>
+  </si>
+  <si>
+    <t>30, June 2027</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>3, July 2027</t>
+  </si>
+  <si>
+    <t>17, July 2027</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>9, Aug 2027</t>
+  </si>
+  <si>
+    <t>24, Aug 2027</t>
+  </si>
+  <si>
+    <t>11, Sept 2027</t>
+  </si>
+  <si>
+    <t>26, Sept 2027</t>
+  </si>
+  <si>
+    <t>6, Oct 2027</t>
+  </si>
+  <si>
+    <t>21, Oct 2027</t>
+  </si>
+  <si>
+    <t>4, Nov 2027</t>
+  </si>
+  <si>
+    <t>19, Nov 2027</t>
+  </si>
+  <si>
+    <t>8, Dec 2027</t>
+  </si>
+  <si>
+    <t>23, Dec 2027</t>
+  </si>
+  <si>
+    <t>15, Jan 2028</t>
+  </si>
+  <si>
+    <t>31, Jan 2028</t>
+  </si>
+  <si>
+    <t>1, March 2027</t>
+  </si>
+  <si>
+    <t>31, Dec 2027</t>
+  </si>
+  <si>
+    <t>10, Jan 2028</t>
+  </si>
+  <si>
+    <t>29, June 2027</t>
+  </si>
+  <si>
+    <t>30, Nov 2027</t>
+  </si>
+  <si>
+    <t>1, May 2027</t>
+  </si>
+  <si>
+    <t>2, May 2027</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +356,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -249,12 +404,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -270,10 +431,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -828,10 +985,248 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E729E6-B817-4BDC-95CB-9675120E71A6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/test/java/resources/data.xlsx
+++ b/src/test/java/resources/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2497728_cognizant_com/Documents/Documents/AutomationProject/PolicyBazzarAutomationHackathon/src/test/java/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2497745_cognizant_com/Documents/Documents/HackathonProject/InsuranceAutomationHackathon/src/test/java/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3518FAB1-7ACA-4389-A734-02A703757C13}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC801BE-855C-4417-94E3-A354BC8867E2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Car" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
   <si>
     <t>CityOfRegistration</t>
   </si>
@@ -68,9 +68,6 @@
     <t>maruti01@gmail.com</t>
   </si>
   <si>
-    <t>KARNATAKA-BENGALURU</t>
-  </si>
-  <si>
     <t>TATA</t>
   </si>
   <si>
@@ -92,102 +89,6 @@
     <t>mahindra01@gmail.com</t>
   </si>
   <si>
-    <t>GUJARAT-AHMEDABAD</t>
-  </si>
-  <si>
-    <t>HYUNDAI - GETZ PRIME GVS (1086CC)</t>
-  </si>
-  <si>
-    <t>hyundai02@gmail.com</t>
-  </si>
-  <si>
-    <t>KERALA-KOCHI</t>
-  </si>
-  <si>
-    <t>TATA MOTORS - TATA ESTATE (1948CC)</t>
-  </si>
-  <si>
-    <t>tata02@gmail.com</t>
-  </si>
-  <si>
-    <t>RAJASTHAN-JAIPUR</t>
-  </si>
-  <si>
-    <t>MARUTI - SX4 1.6 VXI (1586CC)</t>
-  </si>
-  <si>
-    <t>maruti02@gmail.com</t>
-  </si>
-  <si>
-    <t>TELANGANA-HYDERABAD</t>
-  </si>
-  <si>
-    <t>MAHINDRA RENAULT PVT LTD. - LOGAN DIESEL K9K PS E2 5 RT AIR BAG (1461CC)</t>
-  </si>
-  <si>
-    <t>mahindra02@gmail.com</t>
-  </si>
-  <si>
-    <t>WEST BENGAL-KOLKATA</t>
-  </si>
-  <si>
-    <t>HYUNDAI - SONATA EMBERA CRDI (1991CC)</t>
-  </si>
-  <si>
-    <t>hyundai03@gmail.com</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH-INDORE</t>
-  </si>
-  <si>
-    <t>TATA MOTORS - INDIGO MARINA GLE (1405CC)</t>
-  </si>
-  <si>
-    <t>tata03@gmail.com</t>
-  </si>
-  <si>
-    <t>UTTAR PRADESH-LUCKNOW</t>
-  </si>
-  <si>
-    <t>MARUTI - SX4 1.6 ZXI (1586CC)</t>
-  </si>
-  <si>
-    <t>maruti03@gmail.com</t>
-  </si>
-  <si>
-    <t>PUNJAB-CHANDIGARH</t>
-  </si>
-  <si>
-    <t>TATA MOTORS - INDIGO MARINA DICOR LX (1405CC)</t>
-  </si>
-  <si>
-    <t>tata04@gmail.com</t>
-  </si>
-  <si>
-    <t>ODISHA-BHUBANESWAR</t>
-  </si>
-  <si>
-    <t>HYUNDAI - GETZ PRIME GLE (1086CC)</t>
-  </si>
-  <si>
-    <t>hyundai04@gmail.com</t>
-  </si>
-  <si>
-    <t>BIHAR-PATNA</t>
-  </si>
-  <si>
-    <t>MAHINDRA RENAULT PVT LTD. - LOGAN PETROL K7M PS E2 5 JS AIR BAG (1598CC)</t>
-  </si>
-  <si>
-    <t>mahindra03@gmail.com</t>
-  </si>
-  <si>
-    <t>ASSAM-GUWAHATI</t>
-  </si>
-  <si>
-    <t>tata05@gmail.com</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
@@ -333,6 +234,9 @@
   </si>
   <si>
     <t>2, May 2027</t>
+  </si>
+  <si>
+    <t>KARNATAKA-BANGALORE</t>
   </si>
 </sst>
 </file>
@@ -431,6 +335,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -696,13 +604,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.54296875" customWidth="1"/>
     <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="81.1796875" customWidth="1"/>
-    <col min="4" max="4" width="39.453125" customWidth="1"/>
+    <col min="4" max="4" width="49.453125" customWidth="1"/>
     <col min="5" max="5" width="44.1796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -759,223 +667,36 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D4" s="2">
         <v>9876543212</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="D5" s="2">
         <v>9876543213</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2">
-        <v>9876543214</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2">
-        <v>9876543215</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2">
-        <v>9876543216</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="2">
-        <v>9876543217</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="2">
-        <v>9876543218</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="2">
-        <v>9876543219</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="2">
-        <v>9876543220</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="2">
-        <v>9876543221</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="2">
-        <v>9876543222</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="2">
-        <v>9876543223</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="2">
-        <v>9876543224</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -995,233 +716,233 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/resources/data.xlsx
+++ b/src/test/java/resources/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2497728_cognizant_com/Documents/Documents/AutomationProject/PolicyBazzarAutomationHackathon/src/test/java/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3518FAB1-7ACA-4389-A734-02A703757C13}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_F25DC773A252ABDACC104848599D7EA05BDE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6ABFF5A-2F34-4CE4-8CF5-8D6918B2168C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
   <si>
     <t>CityOfRegistration</t>
   </si>
@@ -333,6 +333,60 @@
   </si>
   <si>
     <t>2, May 2027</t>
+  </si>
+  <si>
+    <t>TravellerCount</t>
+  </si>
+  <si>
+    <t>Traveller Ages</t>
+  </si>
+  <si>
+    <t>22,21</t>
+  </si>
+  <si>
+    <t>22,58,33,76,49</t>
+  </si>
+  <si>
+    <t>67,29</t>
+  </si>
+  <si>
+    <t>18,54,73,41</t>
+  </si>
+  <si>
+    <t>35,61,27,52,79</t>
+  </si>
+  <si>
+    <t>48,69,21</t>
+  </si>
+  <si>
+    <t>57,32</t>
+  </si>
+  <si>
+    <t>74,25,63,44</t>
+  </si>
+  <si>
+    <t>28,80,51,39,66</t>
+  </si>
+  <si>
+    <t>23,72,55</t>
+  </si>
+  <si>
+    <t>46,68</t>
+  </si>
+  <si>
+    <t>31,77,53,20</t>
+  </si>
+  <si>
+    <t>70,26,43,58,34</t>
+  </si>
+  <si>
+    <t>81,37,22</t>
+  </si>
+  <si>
+    <t>50,75</t>
+  </si>
+  <si>
+    <t>60,29,83,47</t>
   </si>
 </sst>
 </file>
@@ -404,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -415,6 +469,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,6 +497,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -985,15 +1055,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E729E6-B817-4BDC-95CB-9675120E71A6}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7265625" customWidth="1"/>
     <col min="2" max="2" width="13.54296875" customWidth="1"/>
     <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>53</v>
       </c>
@@ -1003,8 +1075,14 @@
       <c r="C1" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>56</v>
       </c>
@@ -1014,8 +1092,14 @@
       <c r="C2" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>59</v>
       </c>
@@ -1025,8 +1109,14 @@
       <c r="C3" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>62</v>
       </c>
@@ -1036,8 +1126,14 @@
       <c r="C4" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4" s="4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
@@ -1047,8 +1143,14 @@
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>56</v>
       </c>
@@ -1058,8 +1160,14 @@
       <c r="C6" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6" s="4">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>70</v>
       </c>
@@ -1069,8 +1177,14 @@
       <c r="C7" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>73</v>
       </c>
@@ -1080,8 +1194,14 @@
       <c r="C8" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8" s="4">
+        <v>5</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>76</v>
       </c>
@@ -1091,8 +1211,14 @@
       <c r="C9" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9" s="4">
+        <v>3</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>79</v>
       </c>
@@ -1102,8 +1228,14 @@
       <c r="C10" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>82</v>
       </c>
@@ -1113,8 +1245,14 @@
       <c r="C11" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11" s="4">
+        <v>4</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>56</v>
       </c>
@@ -1124,8 +1262,14 @@
       <c r="C12" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12" s="4">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>59</v>
       </c>
@@ -1135,8 +1279,14 @@
       <c r="C13" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>62</v>
       </c>
@@ -1146,8 +1296,14 @@
       <c r="C14" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>65</v>
       </c>
@@ -1157,8 +1313,14 @@
       <c r="C15" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>56</v>
       </c>
@@ -1168,8 +1330,14 @@
       <c r="C16" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -1179,8 +1347,14 @@
       <c r="C17" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="4">
+        <v>5</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>62</v>
       </c>
@@ -1190,8 +1364,14 @@
       <c r="C18" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>73</v>
       </c>
@@ -1201,8 +1381,14 @@
       <c r="C19" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>82</v>
       </c>
@@ -1212,8 +1398,14 @@
       <c r="C20" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>79</v>
       </c>
@@ -1222,6 +1414,12 @@
       </c>
       <c r="C21" s="4" t="s">
         <v>101</v>
+      </c>
+      <c r="D21" s="4">
+        <v>4</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
